--- a/output/stock_quant_scores/GOOGL_info.xlsx
+++ b/output/stock_quant_scores/GOOGL_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FT2"/>
+  <dimension ref="A1:FX2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1076,230 +1076,250 @@
       </c>
       <c r="EA1" s="1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>dividendDate</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>epsCurrentYear</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>priceEpsCurrentYear</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>averageAnalystRating</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>dividendDate</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="FD1" s="1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="FQ1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="FR1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="FS1" s="1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="FT1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="FU1" s="1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="FH1" s="1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="FP1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="FQ1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="FR1" s="1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="FS1" s="1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="FT1" s="1" t="inlineStr">
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1420,34 +1440,34 @@
         <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>251.66</v>
+        <v>245.757</v>
       </c>
       <c r="AC2" t="n">
-        <v>251.66</v>
+        <v>246.97</v>
       </c>
       <c r="AD2" t="n">
-        <v>246.44</v>
+        <v>245.97</v>
       </c>
       <c r="AE2" t="n">
-        <v>252.3501</v>
+        <v>249.42</v>
       </c>
       <c r="AF2" t="n">
-        <v>251.66</v>
+        <v>245.757</v>
       </c>
       <c r="AG2" t="n">
-        <v>251.66</v>
+        <v>246.97</v>
       </c>
       <c r="AH2" t="n">
-        <v>246.44</v>
+        <v>245.97</v>
       </c>
       <c r="AI2" t="n">
-        <v>252.3501</v>
+        <v>249.42</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.84</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="AL2" t="n">
         <v>1757289600</v>
@@ -1459,40 +1479,40 @@
         <v>1.011</v>
       </c>
       <c r="AO2" t="n">
-        <v>26.396166</v>
+        <v>26.311632</v>
       </c>
       <c r="AP2" t="n">
-        <v>27.662947</v>
+        <v>27.515625</v>
       </c>
       <c r="AQ2" t="n">
-        <v>18535253</v>
+        <v>18343782</v>
       </c>
       <c r="AR2" t="n">
-        <v>18535253</v>
+        <v>18343782</v>
       </c>
       <c r="AS2" t="n">
-        <v>38110533</v>
+        <v>36559933</v>
       </c>
       <c r="AT2" t="n">
-        <v>36481560</v>
+        <v>35003170</v>
       </c>
       <c r="AU2" t="n">
-        <v>36481560</v>
+        <v>35003170</v>
       </c>
       <c r="AV2" t="n">
-        <v>246.03</v>
+        <v>234.58</v>
       </c>
       <c r="AW2" t="n">
-        <v>250.97</v>
+        <v>246.62</v>
       </c>
       <c r="AX2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AY2" t="n">
         <v>4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3001255460864</v>
+        <v>2985129672704</v>
       </c>
       <c r="BA2" t="n">
         <v>140.53</v>
@@ -1507,19 +1527,19 @@
         <v>2.401401</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.080947</v>
+        <v>8.037527000000001</v>
       </c>
       <c r="BF2" t="n">
-        <v>211.557</v>
+        <v>215.3754</v>
       </c>
       <c r="BG2" t="n">
-        <v>183.9437</v>
+        <v>185.03246</v>
       </c>
       <c r="BH2" t="n">
         <v>1.01</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.004013351</v>
+        <v>0.0041097505</v>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
@@ -1530,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>2990095990784</v>
+        <v>2928174694400</v>
       </c>
       <c r="BM2" t="n">
         <v>0.31118</v>
@@ -1542,40 +1562,40 @@
         <v>5817000000</v>
       </c>
       <c r="BP2" t="n">
-        <v>55471936</v>
+        <v>67329048</v>
       </c>
       <c r="BQ2" t="n">
-        <v>57377636</v>
+        <v>59170664</v>
       </c>
       <c r="BR2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.0046</v>
+        <v>0.0056</v>
       </c>
       <c r="BU2" t="n">
         <v>0.0025799999</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.80918</v>
+        <v>0.80931</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.0095</v>
+        <v>0.0116</v>
       </c>
       <c r="BY2" t="n">
-        <v>12108672177</v>
+        <v>12108095887</v>
       </c>
       <c r="BZ2" t="n">
         <v>29.983</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.266685000000001</v>
+        <v>8.222659</v>
       </c>
       <c r="CB2" t="n">
         <v>1735603200</v>
@@ -1593,7 +1613,7 @@
         <v>115572998144</v>
       </c>
       <c r="CG2" t="n">
-        <v>9.390000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="CH2" t="n">
         <v>8.960000000000001</v>
@@ -1607,16 +1627,16 @@
         <v>1658102400</v>
       </c>
       <c r="CK2" t="n">
-        <v>8.051</v>
+        <v>7.884</v>
       </c>
       <c r="CL2" t="n">
-        <v>21.23</v>
+        <v>20.791</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.5583627</v>
+        <v>0.486524</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CO2" t="n">
         <v>0.21</v>
@@ -1630,7 +1650,7 @@
         </is>
       </c>
       <c r="CR2" t="n">
-        <v>247.86</v>
+        <v>246.54</v>
       </c>
       <c r="CS2" t="n">
         <v>300</v>
@@ -1750,169 +1770,181 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="EA2" t="n">
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.318603</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>246.54</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>0.032449838</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>246.62</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0.08000183</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>0.78299</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>245.97 - 249.42</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>NasdaqGS</t>
+        </is>
+      </c>
+      <c r="EK2" t="n">
+        <v>36559933</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>106.009995</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>0.7543585</v>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>140.53 - 256.0</t>
+        </is>
+      </c>
+      <c r="EO2" t="n">
+        <v>-9.460006999999999</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>-0.03695315</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>48.652397</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>1757894400</v>
+      </c>
+      <c r="ES2" t="n">
         <v>1753300800</v>
       </c>
-      <c r="EB2" t="n">
+      <c r="ET2" t="n">
         <v>1753300800</v>
       </c>
-      <c r="EC2" t="n">
+      <c r="EU2" t="n">
         <v>1753300800</v>
       </c>
-      <c r="ED2" t="n">
+      <c r="EV2" t="n">
         <v>1753302600</v>
       </c>
-      <c r="EE2" t="n">
+      <c r="EW2" t="n">
         <v>1753302600</v>
       </c>
-      <c r="EF2" t="b">
+      <c r="EX2" t="b">
         <v>0</v>
       </c>
-      <c r="EG2" t="n">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="EH2" t="n">
+      <c r="EY2" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="EZ2" t="n">
         <v>8.960000000000001</v>
       </c>
-      <c r="EI2" t="n">
+      <c r="FA2" t="n">
         <v>9.94481</v>
       </c>
-      <c r="EJ2" t="n">
-        <v>24.923553</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>36.302994</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>0.1715991</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>63.916306</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>0.34747756</v>
-      </c>
-      <c r="EO2" t="n">
+      <c r="FB2" t="n">
+        <v>24.79082</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>31.164597</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>0.14469896</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>61.507538</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>0.33241487</v>
+      </c>
+      <c r="FG2" t="n">
         <v>15</v>
       </c>
-      <c r="EP2" t="n">
+      <c r="FH2" t="n">
         <v>0</v>
       </c>
-      <c r="EQ2" t="inlineStr">
+      <c r="FI2" t="inlineStr">
         <is>
           <t>1.5 - Buy</t>
         </is>
       </c>
-      <c r="ER2" t="n">
-        <v>-3.800003</v>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>246.44 - 252.3501</t>
-        </is>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>NasdaqGS</t>
-        </is>
-      </c>
-      <c r="EU2" t="n">
-        <v>38110533</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>107.33</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>0.7637515</v>
-      </c>
-      <c r="EX2" t="inlineStr">
-        <is>
-          <t>140.53 - 256.0</t>
-        </is>
-      </c>
-      <c r="EY2" t="n">
-        <v>-8.139999</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>-0.031796873</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>55.836273</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>1757894400</v>
-      </c>
-      <c r="FC2" t="inlineStr">
+      <c r="FJ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>1092922200000</v>
+      </c>
+      <c r="FL2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="FD2" t="n">
-        <v>1758740008</v>
-      </c>
-      <c r="FE2" t="inlineStr">
-        <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="FF2" t="inlineStr">
-        <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="FG2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="FH2" t="b">
+      <c r="FM2" t="n">
+        <v>1758931199</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>1758916801</v>
+      </c>
+      <c r="FO2" t="inlineStr">
+        <is>
+          <t>NMS</t>
+        </is>
+      </c>
+      <c r="FP2" t="inlineStr">
+        <is>
+          <t>finmb_29096</t>
+        </is>
+      </c>
+      <c r="FQ2" t="inlineStr">
+        <is>
+          <t>America/New_York</t>
+        </is>
+      </c>
+      <c r="FR2" t="inlineStr">
+        <is>
+          <t>EDT</t>
+        </is>
+      </c>
+      <c r="FS2" t="n">
+        <v>-14400000</v>
+      </c>
+      <c r="FT2" t="inlineStr">
+        <is>
+          <t>us_market</t>
+        </is>
+      </c>
+      <c r="FU2" t="b">
         <v>0</v>
       </c>
-      <c r="FI2" t="inlineStr">
-        <is>
-          <t>NMS</t>
-        </is>
-      </c>
-      <c r="FJ2" t="inlineStr">
-        <is>
-          <t>finmb_29096</t>
-        </is>
-      </c>
-      <c r="FK2" t="inlineStr">
-        <is>
-          <t>America/New_York</t>
-        </is>
-      </c>
-      <c r="FL2" t="inlineStr">
-        <is>
-          <t>EDT</t>
-        </is>
-      </c>
-      <c r="FM2" t="n">
-        <v>-14400000</v>
-      </c>
-      <c r="FN2" t="inlineStr">
-        <is>
-          <t>us_market</t>
-        </is>
-      </c>
-      <c r="FO2" t="b">
+      <c r="FV2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="FW2" t="b">
         <v>0</v>
       </c>
-      <c r="FP2" t="n">
-        <v>-1.509975</v>
-      </c>
-      <c r="FQ2" t="n">
-        <v>247.86</v>
-      </c>
-      <c r="FR2" t="b">
-        <v>1</v>
-      </c>
-      <c r="FS2" t="n">
-        <v>1092922200000</v>
-      </c>
-      <c r="FT2" t="n">
-        <v>1.712</v>
+      <c r="FX2" t="n">
+        <v>1.6772</v>
       </c>
     </row>
   </sheetData>
